--- a/clusia_panomics_database/metadata.xlsx
+++ b/clusia_panomics_database/metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maestro/ucloud/Shared/Clusia/ClusiaDB/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maestro/git/Clusia/clusia_panomics_database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B80EBE-F417-844A-AF70-0ECD7AA8860A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0619E0A-EA75-6441-8AF3-4C711B77EA1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1040" yWindow="-20460" windowWidth="34200" windowHeight="20100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1500" yWindow="780" windowWidth="29040" windowHeight="19420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Genes" sheetId="1" r:id="rId1"/>
@@ -154,7 +154,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1389" uniqueCount="853">
   <si>
     <t>pathway</t>
   </si>
@@ -1500,9 +1500,6 @@
     <t>SID</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
     <t>FH5T13</t>
   </si>
   <si>
@@ -2001,9 +1998,6 @@
     <t>PGM1*</t>
   </si>
   <si>
-    <t>PGM1 (not sure)</t>
-  </si>
-  <si>
     <t>PHS1 (fragmented)</t>
   </si>
   <si>
@@ -2190,9 +2184,6 @@
     <t>OG0000623</t>
   </si>
   <si>
-    <t>ADG</t>
-  </si>
-  <si>
     <t>OG0056186</t>
   </si>
   <si>
@@ -2254,13 +2245,481 @@
   </si>
   <si>
     <t>OG0009445</t>
+  </si>
+  <si>
+    <t>Sample</t>
+  </si>
+  <si>
+    <t>VBCF.SID</t>
+  </si>
+  <si>
+    <t>OG0034738</t>
+  </si>
+  <si>
+    <t>OG0022465</t>
+  </si>
+  <si>
+    <t>OG0033431</t>
+  </si>
+  <si>
+    <t>PGM (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0058170</t>
+  </si>
+  <si>
+    <t>OG0000791</t>
+  </si>
+  <si>
+    <t>PPase/AVP1 (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0032842</t>
+  </si>
+  <si>
+    <t>GWD2 (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0058111</t>
+  </si>
+  <si>
+    <t>GWD3/PWD (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0038743</t>
+  </si>
+  <si>
+    <t>OG0033535</t>
+  </si>
+  <si>
+    <t>OG0015231</t>
+  </si>
+  <si>
+    <t>OG0017668</t>
+  </si>
+  <si>
+    <t>OG0000224</t>
+  </si>
+  <si>
+    <t>GATA TF (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0016664</t>
+  </si>
+  <si>
+    <t>OG0014273</t>
+  </si>
+  <si>
+    <t>OG0014794</t>
+  </si>
+  <si>
+    <t>OG0005858</t>
+  </si>
+  <si>
+    <t>Cro0.g117165</t>
+  </si>
+  <si>
+    <t>Highly fractionated PEPC4 gene fragment</t>
+  </si>
+  <si>
+    <t>OG0057161</t>
+  </si>
+  <si>
+    <t>AGPase/APL3 (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0033735</t>
+  </si>
+  <si>
+    <t>SBE1 (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0022448</t>
+  </si>
+  <si>
+    <t>OG0011469</t>
+  </si>
+  <si>
+    <t>SBE3 (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0057298</t>
+  </si>
+  <si>
+    <t>SS1 (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0025627</t>
+  </si>
+  <si>
+    <t>SS via EC 2.4.1.21, Cmi matches SS4 gene (highly fragmented)</t>
+  </si>
+  <si>
+    <t>OG0025034</t>
+  </si>
+  <si>
+    <t>OG0007842</t>
+  </si>
+  <si>
+    <t>AMY3 (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0041756</t>
+  </si>
+  <si>
+    <t>AMY PCMP-E74 via EC 3.2.1.1</t>
+  </si>
+  <si>
+    <t>OG0034313</t>
+  </si>
+  <si>
+    <t>AGPase/ADG</t>
+  </si>
+  <si>
+    <t>OG0055838</t>
+  </si>
+  <si>
+    <t>OG0009190</t>
+  </si>
+  <si>
+    <t>DPE2 (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0020225</t>
+  </si>
+  <si>
+    <t>GPT2 (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0001519</t>
+  </si>
+  <si>
+    <t>OG0020999</t>
+  </si>
+  <si>
+    <t>OG0058199</t>
+  </si>
+  <si>
+    <t>OG0016526</t>
+  </si>
+  <si>
+    <t>OG0003941</t>
+  </si>
+  <si>
+    <t>PGlyM1|2 (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0016849</t>
+  </si>
+  <si>
+    <t>PEPC1 (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0020641</t>
+  </si>
+  <si>
+    <t>OG0001285</t>
+  </si>
+  <si>
+    <t>OG0034252</t>
+  </si>
+  <si>
+    <t>PEPC-kinase (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0002380</t>
+  </si>
+  <si>
+    <t>OG0058217</t>
+  </si>
+  <si>
+    <t>OG0015354</t>
+  </si>
+  <si>
+    <t>NAD-ME1 (fragmented)</t>
+  </si>
+  <si>
+    <t>NAD-ME2 (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0031710</t>
+  </si>
+  <si>
+    <t>OG0004504</t>
+  </si>
+  <si>
+    <t>OG0015417</t>
+  </si>
+  <si>
+    <t>OG0042509</t>
+  </si>
+  <si>
+    <t>OG0000843</t>
+  </si>
+  <si>
+    <t>NADP-ME (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0018723</t>
+  </si>
+  <si>
+    <t>OG0002610</t>
+  </si>
+  <si>
+    <t>PEP-CK1 (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0024773</t>
+  </si>
+  <si>
+    <t>PUMP (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0013834</t>
+  </si>
+  <si>
+    <t>OG0001880</t>
+  </si>
+  <si>
+    <t>MDH (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0016197</t>
+  </si>
+  <si>
+    <t>MDHG (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0023432</t>
+  </si>
+  <si>
+    <t>OG0027534</t>
+  </si>
+  <si>
+    <t>MMDH (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0004470</t>
+  </si>
+  <si>
+    <t>OG0034376</t>
+  </si>
+  <si>
+    <t>OG0042632</t>
+  </si>
+  <si>
+    <t>MDH via EC 1.1.1.37, hypothetical and highly fragmented</t>
+  </si>
+  <si>
+    <t>OG0042529</t>
+  </si>
+  <si>
+    <t>ADG2A fragment via EC 2.7.7.27</t>
+  </si>
+  <si>
+    <t>Cmu00.g22380</t>
+  </si>
+  <si>
+    <t>Cmu00.g22394</t>
+  </si>
+  <si>
+    <t>Cmu00.g22395</t>
+  </si>
+  <si>
+    <t>Cmi0.g72889</t>
+  </si>
+  <si>
+    <t>Cro0.g101231</t>
+  </si>
+  <si>
+    <t>Cro0.g116039</t>
+  </si>
+  <si>
+    <t>Cmu00.g12332</t>
+  </si>
+  <si>
+    <t>Cmu00.g12333</t>
+  </si>
+  <si>
+    <t>Cmi0.g23911</t>
+  </si>
+  <si>
+    <t>Cmi0.g27141</t>
+  </si>
+  <si>
+    <t>Cmi0.g51966</t>
+  </si>
+  <si>
+    <t>Cro0.g25751</t>
+  </si>
+  <si>
+    <t>Cro0.g54677</t>
+  </si>
+  <si>
+    <t>Cro0.g83481</t>
+  </si>
+  <si>
+    <t>Cmu00.g20140</t>
+  </si>
+  <si>
+    <t>Cmu00.g20141</t>
+  </si>
+  <si>
+    <t>Cro0.g28883</t>
+  </si>
+  <si>
+    <t>Cmi0.g50698</t>
+  </si>
+  <si>
+    <t>Cmi0.g822</t>
+  </si>
+  <si>
+    <t>Cro0.g86882</t>
+  </si>
+  <si>
+    <t>Cro0.g92313</t>
+  </si>
+  <si>
+    <t>Cro0.g103101</t>
+  </si>
+  <si>
+    <t>Cro0.g110839</t>
+  </si>
+  <si>
+    <t>Cro0.g53021</t>
+  </si>
+  <si>
+    <t>Cro0.g56314</t>
+  </si>
+  <si>
+    <t>Cro0.g99684</t>
+  </si>
+  <si>
+    <t>OG0011622</t>
+  </si>
+  <si>
+    <t>GPT2 (probable)</t>
+  </si>
+  <si>
+    <t>Cro0.g6720</t>
+  </si>
+  <si>
+    <t>Cro0.g124978</t>
+  </si>
+  <si>
+    <t>Cro0.g64536</t>
+  </si>
+  <si>
+    <t>Cmi0.g21665</t>
+  </si>
+  <si>
+    <t>Cmi0.g17404</t>
+  </si>
+  <si>
+    <t>Cmi0.g17405</t>
+  </si>
+  <si>
+    <t>Cro0.g88720</t>
+  </si>
+  <si>
+    <t>Cro0.g24617</t>
+  </si>
+  <si>
+    <t>Cro0.g84829</t>
+  </si>
+  <si>
+    <t>Cro0.g84830</t>
+  </si>
+  <si>
+    <t>Cro0.g84836</t>
+  </si>
+  <si>
+    <t>Cro0.g84839</t>
+  </si>
+  <si>
+    <t>Cro0.g61064</t>
+  </si>
+  <si>
+    <t>Cmi0.g42504</t>
+  </si>
+  <si>
+    <t>Cmu00.g9091</t>
+  </si>
+  <si>
+    <t>Cmi0.g54546</t>
+  </si>
+  <si>
+    <t>Cro0.g46442</t>
+  </si>
+  <si>
+    <t>Cro0.g46445</t>
+  </si>
+  <si>
+    <t>Cro0.g125404</t>
+  </si>
+  <si>
+    <t>Cro0.g43523</t>
+  </si>
+  <si>
+    <t>Cro0.g4504</t>
+  </si>
+  <si>
+    <t>MMDH</t>
+  </si>
+  <si>
+    <t>OG0028658</t>
+  </si>
+  <si>
+    <t>PIF3 TF via UniprotID O80536, highly fragmented family</t>
+  </si>
+  <si>
+    <t>OG0016262</t>
+  </si>
+  <si>
+    <t>OG0000838</t>
+  </si>
+  <si>
+    <t>GBF/GNL TF (fragmented)</t>
+  </si>
+  <si>
+    <t>OG0054193</t>
+  </si>
+  <si>
+    <t>OG0031073</t>
+  </si>
+  <si>
+    <t>OG0056445</t>
+  </si>
+  <si>
+    <t>OG0018279</t>
+  </si>
+  <si>
+    <t>OG0033448</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Cmu00.g23307</t>
+  </si>
+  <si>
+    <t>Cmu00.g15123</t>
+  </si>
+  <si>
+    <t>TCP7</t>
+  </si>
+  <si>
+    <t>Cro0.g53390</t>
+  </si>
+  <si>
+    <t>GN</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2345,6 +2804,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2376,7 +2842,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2410,6 +2876,9 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2718,7 +3187,7 @@
         <v>442</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>2</v>
@@ -2742,18 +3211,18 @@
         <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>240</v>
@@ -2780,13 +3249,13 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>246</v>
@@ -2812,13 +3281,13 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>250</v>
@@ -2844,13 +3313,13 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>254</v>
@@ -2876,13 +3345,13 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>235</v>
@@ -2909,13 +3378,13 @@
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>258</v>
@@ -2941,13 +3410,13 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>263</v>
@@ -2973,7 +3442,7 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>10</v>
@@ -3006,7 +3475,7 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>10</v>
@@ -3039,7 +3508,7 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>10</v>
@@ -3072,7 +3541,7 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>10</v>
@@ -3105,7 +3574,7 @@
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>10</v>
@@ -3138,13 +3607,13 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>207</v>
@@ -3170,13 +3639,13 @@
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>212</v>
@@ -3205,13 +3674,13 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>216</v>
@@ -3238,13 +3707,13 @@
     </row>
     <row r="17" spans="1:22" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>230</v>
@@ -3271,13 +3740,13 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>221</v>
@@ -3306,13 +3775,13 @@
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>226</v>
@@ -3345,7 +3814,7 @@
         <v>10</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>306</v>
@@ -3378,7 +3847,7 @@
         <v>10</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>311</v>
@@ -3410,7 +3879,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>315</v>
@@ -3444,7 +3913,7 @@
         <v>10</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>320</v>
@@ -3476,7 +3945,7 @@
         <v>10</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>288</v>
@@ -3509,7 +3978,7 @@
         <v>10</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>293</v>
@@ -3541,7 +4010,7 @@
         <v>10</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>297</v>
@@ -3572,7 +4041,7 @@
         <v>10</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>301</v>
@@ -3604,7 +4073,7 @@
         <v>10</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>324</v>
@@ -3637,7 +4106,7 @@
         <v>116</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>328</v>
@@ -3667,7 +4136,7 @@
         <v>116</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>332</v>
@@ -3729,7 +4198,7 @@
         <v>10</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>150</v>
@@ -3761,7 +4230,7 @@
         <v>10</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>155</v>
@@ -3793,7 +4262,7 @@
         <v>10</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>159</v>
@@ -3827,7 +4296,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>165</v>
@@ -3859,7 +4328,7 @@
         <v>10</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>171</v>
@@ -3891,7 +4360,7 @@
         <v>10</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>175</v>
@@ -3914,7 +4383,7 @@
       </c>
       <c r="K37" s="6"/>
       <c r="L37" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.2">
@@ -3925,7 +4394,7 @@
         <v>10</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>180</v>
@@ -3988,7 +4457,7 @@
         <v>116</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>188</v>
@@ -4021,7 +4490,7 @@
         <v>116</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>193</v>
@@ -4053,7 +4522,7 @@
         <v>116</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>198</v>
@@ -4086,7 +4555,7 @@
         <v>116</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>202</v>
@@ -4118,13 +4587,13 @@
         <v>116</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>13</v>
@@ -4134,10 +4603,10 @@
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="J44" s="6" t="s">
         <v>581</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>582</v>
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
@@ -4150,7 +4619,7 @@
         <v>10</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>28</v>
@@ -4182,7 +4651,7 @@
         <v>10</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>33</v>
@@ -4214,7 +4683,7 @@
         <v>10</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>37</v>
@@ -4246,7 +4715,7 @@
         <v>10</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>41</v>
@@ -4278,7 +4747,7 @@
         <v>10</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>17</v>
@@ -4310,7 +4779,7 @@
         <v>10</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>23</v>
@@ -4728,7 +5197,7 @@
         <v>10</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>107</v>
@@ -4760,7 +5229,7 @@
         <v>10</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>112</v>
@@ -4792,7 +5261,7 @@
         <v>116</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>117</v>
@@ -4824,7 +5293,7 @@
         <v>116</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>122</v>
@@ -4854,7 +5323,7 @@
         <v>116</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>126</v>
@@ -4885,7 +5354,7 @@
         <v>116</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>130</v>
@@ -4920,7 +5389,7 @@
         <v>116</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>136</v>
@@ -4955,7 +5424,7 @@
         <v>116</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D70" s="8" t="s">
         <v>140</v>
@@ -4984,7 +5453,7 @@
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A71" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>10</v>
@@ -5016,7 +5485,7 @@
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A72" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>10</v>
@@ -5058,7 +5527,7 @@
         <v>10</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>341</v>
@@ -5067,7 +5536,7 @@
         <v>342</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G73" s="6" t="s">
         <v>190</v>
@@ -5092,7 +5561,7 @@
         <v>116</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>337</v>
@@ -5101,7 +5570,7 @@
         <v>338</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>190</v>
@@ -5115,7 +5584,7 @@
       </c>
       <c r="K74" s="6"/>
       <c r="L74" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="75" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -5126,7 +5595,7 @@
         <v>116</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>346</v>
@@ -5135,7 +5604,7 @@
         <v>347</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>190</v>
@@ -5158,7 +5627,7 @@
         <v>351</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>359</v>
@@ -5193,7 +5662,7 @@
         <v>351</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>402</v>
@@ -5228,7 +5697,7 @@
         <v>351</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>430</v>
@@ -5263,7 +5732,7 @@
         <v>351</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>408</v>
@@ -5283,7 +5752,7 @@
         <v>411</v>
       </c>
       <c r="K79" s="7" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L79" s="6" t="s">
         <v>407</v>
@@ -5297,7 +5766,7 @@
         <v>351</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>352</v>
@@ -5331,7 +5800,7 @@
         <v>351</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D81" s="14" t="s">
         <v>365</v>
@@ -5366,7 +5835,7 @@
         <v>351</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>371</v>
@@ -5400,7 +5869,7 @@
         <v>351</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>376</v>
@@ -5434,7 +5903,7 @@
         <v>351</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>382</v>
@@ -5468,7 +5937,7 @@
         <v>351</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>387</v>
@@ -5502,7 +5971,7 @@
         <v>351</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>393</v>
@@ -5537,7 +6006,7 @@
         <v>351</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D87" s="6" t="s">
         <v>393</v>
@@ -5572,7 +6041,7 @@
         <v>351</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>412</v>
@@ -5606,7 +6075,7 @@
         <v>351</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>418</v>
@@ -5640,7 +6109,7 @@
         <v>351</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>424</v>
@@ -5675,7 +6144,7 @@
         <v>351</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>436</v>
@@ -5905,15 +6374,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" customWidth="1"/>
     <col min="2" max="2" width="18.1640625" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.1640625" customWidth="1"/>
     <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="44.1640625" customWidth="1"/>
+    <col min="6" max="6" width="46.83203125" customWidth="1"/>
     <col min="7" max="7" width="3.1640625" customWidth="1"/>
     <col min="8" max="9" width="14.83203125" customWidth="1"/>
     <col min="10" max="10" width="44.5" customWidth="1"/>
@@ -5921,391 +6390,932 @@
   <sheetData>
     <row r="1" spans="1:10" s="22" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>568</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="F1" s="22" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H1" s="22" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="I1" s="22" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J1" s="22" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="16" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="J2" s="16" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>595</v>
+        <v>594</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>720</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>719</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>721</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="16" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>212</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="16" t="s">
-        <v>654</v>
+        <v>706</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>601</v>
+        <v>707</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>644</v>
+        <v>731</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>617</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="16" t="s">
-        <v>656</v>
+        <v>710</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>611</v>
+        <v>707</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>673</v>
+        <v>642</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>674</v>
+        <v>615</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>175</v>
+        <v>600</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>645</v>
+        <v>671</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>618</v>
+        <v>672</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="16" t="s">
-        <v>660</v>
+        <v>708</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>615</v>
+        <v>709</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>675</v>
+        <v>738</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>619</v>
+        <v>737</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="16" t="s">
-        <v>662</v>
+        <v>711</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>288</v>
+        <v>709</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>736</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="16" t="s">
-        <v>685</v>
+        <v>657</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>686</v>
+        <v>656</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>293</v>
+        <v>175</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>643</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>616</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="16" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>81</v>
+        <v>522</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>673</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>617</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="16" t="s">
-        <v>665</v>
+        <v>699</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>81</v>
+        <v>702</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>783</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>784</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
-        <v>666</v>
+        <v>700</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>663</v>
+        <v>656</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>81</v>
+        <v>702</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>785</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>786</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
-        <v>667</v>
+        <v>701</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>608</v>
+        <v>702</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>837</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>838</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
-        <v>669</v>
+        <v>733</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>670</v>
+        <v>734</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>633</v>
+        <v>735</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="16" t="s">
-        <v>671</v>
+        <v>660</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="16" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>678</v>
+        <v>293</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="16" t="s">
-        <v>679</v>
+        <v>740</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>680</v>
+        <v>741</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>576</v>
+        <v>742</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="16" t="s">
-        <v>687</v>
+        <v>743</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>688</v>
+        <v>745</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>171</v>
+        <v>744</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="16" t="s">
-        <v>689</v>
+        <v>746</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>688</v>
+        <v>745</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>171</v>
+        <v>744</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="16" t="s">
-        <v>698</v>
+        <v>747</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>699</v>
+        <v>745</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>159</v>
+        <v>744</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="16" t="s">
-        <v>690</v>
+        <v>813</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>694</v>
+        <v>745</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>695</v>
+        <v>814</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
-        <v>691</v>
+        <v>662</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>694</v>
+        <v>661</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>695</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
-        <v>692</v>
+        <v>663</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>694</v>
+        <v>661</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>695</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
-        <v>693</v>
+        <v>664</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>694</v>
+        <v>661</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>695</v>
+        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="16" t="s">
+        <v>759</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>661</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="16" t="s">
+        <v>764</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>661</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="16" t="s">
+        <v>762</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>763</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="16" t="s">
+        <v>765</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>766</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="16" t="s">
+        <v>773</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>774</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="16" t="s">
+        <v>778</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>774</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="16" t="s">
+        <v>665</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="16" t="s">
+        <v>776</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>666</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="16" t="s">
+        <v>779</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>781</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="16" t="s">
+        <v>782</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>781</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="16" t="s">
+        <v>667</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>668</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="16" t="s">
+        <v>724</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>668</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="16" t="s">
+        <v>726</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>727</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="16" t="s">
+        <v>654</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>655</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="16" t="s">
+        <v>729</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>655</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="16" t="s">
+        <v>669</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>670</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="16" t="s">
+        <v>674</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>675</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="16" t="s">
+        <v>722</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>675</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="16" t="s">
+        <v>703</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>704</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="16" t="s">
+        <v>676</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>677</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="16" t="s">
+        <v>771</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>677</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="16" t="s">
+        <v>684</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>685</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>685</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="16" t="s">
+        <v>695</v>
+      </c>
+      <c r="B51" s="16" t="s">
         <v>696</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>697</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>527</v>
+      <c r="C51" s="16" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="16" t="s">
+        <v>748</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>749</v>
+      </c>
+      <c r="C52" s="16" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="16" t="s">
+        <v>687</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="C53" s="16" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="16" t="s">
+        <v>689</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="C55" s="16" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="16" t="s">
+        <v>690</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="16" t="s">
+        <v>693</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>694</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="16" t="s">
+        <v>718</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>719</v>
+      </c>
+      <c r="C58" s="16" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="16" t="s">
+        <v>751</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>754</v>
+      </c>
+      <c r="C59" s="16" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="16" t="s">
+        <v>753</v>
+      </c>
+      <c r="B60" s="16" t="s">
+        <v>754</v>
+      </c>
+      <c r="C60" s="16" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="16" t="s">
+        <v>755</v>
+      </c>
+      <c r="B61" s="16" t="s">
+        <v>757</v>
+      </c>
+      <c r="C61" s="16" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>757</v>
+      </c>
+      <c r="C62" s="16" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="16" t="s">
+        <v>768</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>769</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="16" t="s">
+        <v>839</v>
+      </c>
+      <c r="B64" s="16" t="s">
+        <v>840</v>
+      </c>
+      <c r="C64" s="16" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="16" t="s">
+        <v>842</v>
+      </c>
+      <c r="B65" s="16" t="s">
+        <v>840</v>
+      </c>
+      <c r="C65" s="16" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="16" t="s">
+        <v>843</v>
+      </c>
+      <c r="B66" s="16" t="s">
+        <v>840</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="16" t="s">
+        <v>844</v>
+      </c>
+      <c r="B67" s="16" t="s">
+        <v>840</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="16" t="s">
+        <v>845</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>840</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="16" t="s">
+        <v>846</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>840</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="16" t="s">
+        <v>712</v>
+      </c>
+      <c r="B70" s="16" t="s">
+        <v>714</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="16" t="s">
+        <v>713</v>
+      </c>
+      <c r="B71" s="16" t="s">
+        <v>714</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="16" t="s">
+        <v>716</v>
+      </c>
+      <c r="B72" s="16" t="s">
+        <v>714</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="16" t="s">
+        <v>717</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>714</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>715</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
@@ -6313,7 +7323,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" customWidth="1"/>
@@ -6322,71 +7332,117 @@
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" style="4" customWidth="1"/>
     <col min="6" max="6" width="3.1640625" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="7.83203125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="9" max="9" width="3.1640625" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="11" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="3.1640625" customWidth="1"/>
+    <col min="13" max="13" width="8" customWidth="1"/>
+    <col min="14" max="14" width="7.83203125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="22" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" s="22" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="22" t="s">
+        <v>601</v>
+      </c>
+      <c r="B1" s="22" t="s">
         <v>602</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>603</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>596</v>
-      </c>
-      <c r="G1" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>678</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>602</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>678</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>847</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>7710</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D2" s="16">
         <v>59</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G2" s="16" t="s">
+        <v>804</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16" t="s">
+        <v>848</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16" t="s">
+        <v>531</v>
+      </c>
+      <c r="N2" s="17" t="s">
         <v>532</v>
       </c>
-      <c r="H2" s="17" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>63671</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D3" s="16">
         <v>8922</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="G3" s="16" t="s">
+        <v>805</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16" t="s">
+        <v>849</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="N3" s="17" t="s">
         <v>558</v>
       </c>
-      <c r="H3" s="17" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="16">
         <v>4403</v>
       </c>
@@ -6396,13 +7452,21 @@
       <c r="D4" s="16"/>
       <c r="E4" s="17"/>
       <c r="G4" s="16" t="s">
-        <v>558</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <v>806</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="M4" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="N4" s="17" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="16">
         <v>13183</v>
       </c>
@@ -6412,570 +7476,934 @@
       <c r="D5" s="16"/>
       <c r="E5" s="17"/>
       <c r="G5" s="16" t="s">
+        <v>807</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>240</v>
+      </c>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="M5" s="16" t="s">
+        <v>533</v>
+      </c>
+      <c r="N5" s="17" t="s">
         <v>534</v>
       </c>
-      <c r="H5" s="17" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="16">
         <v>5754</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D6" s="16"/>
       <c r="E6" s="17"/>
       <c r="G6" s="16" t="s">
+        <v>787</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="J6" s="16"/>
+      <c r="K6" s="16"/>
+      <c r="M6" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="N6" s="17" t="s">
         <v>536</v>
       </c>
-      <c r="H6" s="17" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="16">
         <v>9450</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D7" s="16"/>
       <c r="E7" s="17"/>
       <c r="G7" s="16" t="s">
+        <v>788</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="J7" s="16"/>
+      <c r="K7" s="16"/>
+      <c r="M7" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="N7" s="17" t="s">
         <v>538</v>
       </c>
-      <c r="H7" s="17" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
         <v>30051</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D8" s="16"/>
       <c r="E8" s="17"/>
       <c r="G8" s="16" t="s">
+        <v>789</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="M8" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="N8" s="17" t="s">
         <v>540</v>
       </c>
-      <c r="H8" s="17" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="16">
         <v>41962</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="D9" s="16"/>
       <c r="E9" s="17"/>
       <c r="G9" s="16" t="s">
+        <v>790</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="M9" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="N9" s="17" t="s">
         <v>542</v>
       </c>
-      <c r="H9" s="17" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="16">
         <v>12441</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D10" s="16"/>
       <c r="E10" s="17"/>
       <c r="G10" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="M10" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="N10" s="17" t="s">
         <v>544</v>
       </c>
-      <c r="H10" s="17" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="16">
         <v>11086</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D11" s="16"/>
       <c r="E11" s="17"/>
       <c r="G11" s="16" t="s">
+        <v>792</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="M11" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="N11" s="17" t="s">
         <v>546</v>
       </c>
-      <c r="H11" s="17" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="16">
         <v>14320</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D12" s="16"/>
       <c r="E12" s="17"/>
       <c r="G12" s="16" t="s">
+        <v>801</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>613</v>
+      </c>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="M12" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="N12" s="17" t="s">
         <v>548</v>
       </c>
-      <c r="H12" s="17" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="16">
         <v>14439</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D13" s="16"/>
       <c r="E13" s="17"/>
       <c r="G13" s="16" t="s">
+        <v>802</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="M13" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="N13" s="17" t="s">
         <v>550</v>
       </c>
-      <c r="H13" s="17" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="16">
         <v>9302</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D14" s="16"/>
       <c r="E14" s="17"/>
       <c r="G14" s="16" t="s">
+        <v>803</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="J14" s="16"/>
+      <c r="K14" s="16"/>
+      <c r="M14" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="N14" s="17" t="s">
         <v>552</v>
       </c>
-      <c r="H14" s="17" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="16">
         <v>6691</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D15" s="16"/>
       <c r="E15" s="17"/>
       <c r="G15" s="16" t="s">
+        <v>793</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>620</v>
+      </c>
+      <c r="J15" s="16"/>
+      <c r="K15" s="16"/>
+      <c r="M15" s="16" t="s">
+        <v>553</v>
+      </c>
+      <c r="N15" s="17" t="s">
         <v>554</v>
       </c>
-      <c r="H15" s="17" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="16">
         <v>32848</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="17"/>
       <c r="G16" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>620</v>
+      </c>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="M16" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>556</v>
       </c>
-      <c r="H16" s="17" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="16">
         <v>9772</v>
       </c>
       <c r="B17" s="16" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G17" s="16" t="s">
+        <v>795</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>620</v>
+      </c>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="16">
         <v>3952</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G18" s="16" t="s">
+        <v>796</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>620</v>
+      </c>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="16">
         <v>3953</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+        <v>613</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>797</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>620</v>
+      </c>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="16">
         <v>30931</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+        <v>613</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>798</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>620</v>
+      </c>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="16">
         <v>7184</v>
       </c>
       <c r="B21" s="16" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G21" s="16" t="s">
+        <v>799</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>620</v>
+      </c>
+      <c r="J21" s="16"/>
+      <c r="K21" s="16"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="16">
         <v>7185</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G22" s="16" t="s">
+        <v>800</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>620</v>
+      </c>
+      <c r="J22" s="16"/>
+      <c r="K22" s="16"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="16">
         <v>9598</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G23" s="16" t="s">
+        <v>808</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="J23" s="16"/>
+      <c r="K23" s="16"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="16">
         <v>9020</v>
       </c>
       <c r="B24" s="16" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G24" s="16" t="s">
+        <v>809</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="J24" s="16"/>
+      <c r="K24" s="16"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="16">
         <v>63191</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+        <v>620</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>810</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="J25" s="16"/>
+      <c r="K25" s="16"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="16">
         <v>63192</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+        <v>620</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>811</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="16">
         <v>11671</v>
       </c>
       <c r="B27" s="16" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G27" s="16" t="s">
+        <v>812</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="J27" s="16"/>
+      <c r="K27" s="16"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="16">
         <v>12105</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G28" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="16">
         <v>16324</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+        <v>526</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>816</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="16">
         <v>3835</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+        <v>526</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="J30" s="16"/>
+      <c r="K30" s="16"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="16">
         <v>36594</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+        <v>526</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>818</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>526</v>
+      </c>
+      <c r="J31" s="16"/>
+      <c r="K31" s="16"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="16">
         <v>11329</v>
       </c>
       <c r="B32" s="16" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G32" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>635</v>
+      </c>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="16">
         <v>34343</v>
       </c>
       <c r="B33" s="16" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G33" s="16" t="s">
+        <v>820</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>635</v>
+      </c>
+      <c r="J33" s="16"/>
+      <c r="K33" s="16"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="16">
         <v>17533</v>
       </c>
       <c r="B34" s="16" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G34" s="16" t="s">
+        <v>821</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>635</v>
+      </c>
+      <c r="J34" s="16"/>
+      <c r="K34" s="16"/>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="16">
         <v>34032</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+        <v>618</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>822</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>636</v>
+      </c>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="16">
         <v>46596</v>
       </c>
       <c r="B36" s="16" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+        <v>618</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>823</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>636</v>
+      </c>
+      <c r="J36" s="16"/>
+      <c r="K36" s="16"/>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="16">
         <v>8886</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+        <v>619</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>824</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>636</v>
+      </c>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="16">
         <v>825</v>
       </c>
       <c r="B38" s="16" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+        <v>622</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>636</v>
+      </c>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="16">
         <v>15314</v>
       </c>
       <c r="B39" s="16" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+        <v>636</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>826</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>636</v>
+      </c>
+      <c r="J39" s="16"/>
+      <c r="K39" s="16"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="16">
         <v>18455</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+        <v>636</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>827</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>629</v>
+      </c>
+      <c r="J40" s="16"/>
+      <c r="K40" s="16"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="16">
         <v>455</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+        <v>629</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>828</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="J41" s="16"/>
+      <c r="K41" s="16"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="16">
         <v>10942</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+        <v>629</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>829</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>626</v>
+      </c>
+      <c r="J42" s="16"/>
+      <c r="K42" s="16"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="16">
         <v>17261</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+        <v>629</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>830</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>626</v>
+      </c>
+      <c r="J43" s="16"/>
+      <c r="K43" s="16"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="16">
         <v>18675</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+        <v>629</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>831</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>626</v>
+      </c>
+      <c r="J44" s="16"/>
+      <c r="K44" s="16"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="16">
         <v>3661</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+        <v>623</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>832</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>626</v>
+      </c>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="16">
         <v>25624</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+        <v>623</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>833</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>836</v>
+      </c>
+      <c r="J46" s="16"/>
+      <c r="K46" s="16"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="16">
         <v>3070</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+        <v>624</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>834</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>836</v>
+      </c>
+      <c r="J47" s="16"/>
+      <c r="K47" s="16"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="16">
         <v>26384</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+        <v>624</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>835</v>
+      </c>
+      <c r="H48" s="16" t="s">
+        <v>836</v>
+      </c>
+      <c r="J48" s="16"/>
+      <c r="K48" s="16"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="16">
         <v>5352</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+        <v>625</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>849</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="16">
         <v>17791</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+        <v>625</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>851</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="16">
         <v>12248</v>
       </c>
       <c r="B51" s="16" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="16">
         <v>15753</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="16">
         <v>6474</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="16">
         <v>23677</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="16">
         <v>14870</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="16">
         <v>43801</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="16">
         <v>15755</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="16">
         <v>39348</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="16">
         <v>13898</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="16">
         <v>27302</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="16">
         <v>54772</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="16">
         <v>63446</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="16">
         <v>63662</v>
       </c>
       <c r="B63" s="16" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="16">
         <v>65693</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
@@ -6983,7 +8411,7 @@
         <v>65917</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
   </sheetData>
@@ -6996,815 +8424,1032 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="7.83203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>697</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>446</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="22" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="C2">
         <v>190967</v>
       </c>
-      <c r="B2" s="4">
+      <c r="D2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="25">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="C3" s="24">
+        <v>190975</v>
+      </c>
+      <c r="D3" s="23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="25">
+        <v>3</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>464</v>
+      </c>
+      <c r="C4" s="24">
+        <v>191049</v>
+      </c>
+      <c r="D4" s="23">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="25">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="C5" s="24">
         <v>190968</v>
       </c>
-      <c r="B3" s="4">
+      <c r="D5" s="23">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="25">
+        <v>5</v>
+      </c>
+      <c r="B6" s="20" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="C6" s="24">
         <v>190969</v>
       </c>
-      <c r="B4" s="4">
+      <c r="D6" s="23">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>453</v>
+      </c>
+      <c r="C7">
+        <v>190972</v>
+      </c>
+      <c r="D7" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>454</v>
+      </c>
+      <c r="C8">
+        <v>190973</v>
+      </c>
+      <c r="D8" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>455</v>
+      </c>
+      <c r="C9">
+        <v>190974</v>
+      </c>
+      <c r="D9" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="25">
+        <v>9</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="C10" s="24">
         <v>190970</v>
       </c>
-      <c r="B5" s="4">
+      <c r="D10" s="23">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="25">
+        <v>10</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>457</v>
+      </c>
+      <c r="C11">
+        <v>190976</v>
+      </c>
+      <c r="D11" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="25">
+        <v>11</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="C12">
+        <v>190977</v>
+      </c>
+      <c r="D12" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="25">
+        <v>12</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>459</v>
+      </c>
+      <c r="C13">
+        <v>190978</v>
+      </c>
+      <c r="D13" s="4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="25">
+        <v>13</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>460</v>
+      </c>
+      <c r="C14">
+        <v>191045</v>
+      </c>
+      <c r="D14" s="4">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="25">
+        <v>14</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>461</v>
+      </c>
+      <c r="C15">
+        <v>191046</v>
+      </c>
+      <c r="D15" s="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="25">
+        <v>15</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>462</v>
+      </c>
+      <c r="C16">
+        <v>191047</v>
+      </c>
+      <c r="D16" s="4">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="25">
+        <v>16</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>463</v>
+      </c>
+      <c r="C17">
+        <v>191048</v>
+      </c>
+      <c r="D17" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="25">
+        <v>17</v>
+      </c>
+      <c r="B18" s="20" t="s">
         <v>452</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="C18" s="24">
         <v>190971</v>
       </c>
-      <c r="B6" s="4">
+      <c r="D18" s="23">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>190972</v>
-      </c>
-      <c r="B7" s="4">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>190973</v>
-      </c>
-      <c r="B8" s="4">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>190974</v>
-      </c>
-      <c r="B9" s="4">
-        <v>8</v>
-      </c>
-      <c r="C9" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>190975</v>
-      </c>
-      <c r="B10" s="4">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>190976</v>
-      </c>
-      <c r="B11" s="4">
-        <v>10</v>
-      </c>
-      <c r="C11" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>190977</v>
-      </c>
-      <c r="B12" s="4">
-        <v>11</v>
-      </c>
-      <c r="C12" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>190978</v>
-      </c>
-      <c r="B13" s="4">
-        <v>12</v>
-      </c>
-      <c r="C13" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>191045</v>
-      </c>
-      <c r="B14" s="4">
-        <v>13</v>
-      </c>
-      <c r="C14" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>191046</v>
-      </c>
-      <c r="B15" s="4">
-        <v>14</v>
-      </c>
-      <c r="C15" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>191047</v>
-      </c>
-      <c r="B16" s="4">
-        <v>15</v>
-      </c>
-      <c r="C16" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>191048</v>
-      </c>
-      <c r="B17" s="4">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>191049</v>
-      </c>
-      <c r="B18" s="4">
-        <v>17</v>
-      </c>
-      <c r="C18" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="25">
+        <v>18</v>
+      </c>
+      <c r="B19" s="20" t="s">
         <v>465</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19">
+      <c r="C19">
         <v>191050</v>
       </c>
-      <c r="B19" s="4">
+      <c r="D19" s="4">
         <v>18</v>
       </c>
-      <c r="C19" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="25">
+        <v>19</v>
+      </c>
+      <c r="B20" s="20" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20">
+      <c r="C20">
         <v>191051</v>
       </c>
-      <c r="B20" s="4">
+      <c r="D20" s="4">
         <v>19</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
         <v>467</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21">
+      <c r="C21">
         <v>191052</v>
       </c>
-      <c r="B21" s="4">
+      <c r="D21" s="4">
         <v>20</v>
       </c>
-      <c r="C21" t="s">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22">
+      <c r="C22">
         <v>191053</v>
       </c>
-      <c r="B22" s="4">
+      <c r="D22" s="4">
         <v>21</v>
       </c>
-      <c r="C22" t="s">
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23">
+      <c r="C23">
         <v>191054</v>
       </c>
-      <c r="B23" s="4">
+      <c r="D23" s="4">
         <v>22</v>
       </c>
-      <c r="C23" t="s">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="4">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
         <v>470</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24">
+      <c r="C24">
         <v>191055</v>
       </c>
-      <c r="B24" s="4">
+      <c r="D24" s="4">
         <v>23</v>
       </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="C25">
         <v>191056</v>
       </c>
-      <c r="B25" s="4">
+      <c r="D25" s="4">
         <v>24</v>
       </c>
-      <c r="C25" t="s">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="4">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26">
+      <c r="C26">
         <v>191057</v>
       </c>
-      <c r="B26" s="4">
+      <c r="D26" s="4">
         <v>25</v>
       </c>
-      <c r="C26" t="s">
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
         <v>473</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27">
+      <c r="C27">
         <v>191058</v>
       </c>
-      <c r="B27" s="4">
+      <c r="D27" s="4">
         <v>26</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="4">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28">
+      <c r="C28">
         <v>191059</v>
       </c>
-      <c r="B28" s="4">
+      <c r="D28" s="4">
         <v>27</v>
       </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
         <v>475</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29">
+      <c r="C29">
         <v>191060</v>
       </c>
-      <c r="B29" s="4">
+      <c r="D29" s="4">
         <v>28</v>
       </c>
-      <c r="C29" t="s">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="4">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
         <v>476</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30">
+      <c r="C30">
         <v>191061</v>
       </c>
-      <c r="B30" s="4">
+      <c r="D30" s="4">
         <v>29</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31">
+      <c r="C31">
         <v>191062</v>
       </c>
-      <c r="B31" s="4">
+      <c r="D31" s="4">
         <v>30</v>
       </c>
-      <c r="C31" t="s">
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="4">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
         <v>478</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32">
+      <c r="C32">
         <v>191063</v>
       </c>
-      <c r="B32" s="4">
+      <c r="D32" s="4">
         <v>31</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33">
+      <c r="C33">
         <v>191064</v>
       </c>
-      <c r="B33" s="4">
+      <c r="D33" s="4">
         <v>32</v>
       </c>
-      <c r="C33" t="s">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="4">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34">
+      <c r="C34">
         <v>191065</v>
       </c>
-      <c r="B34" s="4">
+      <c r="D34" s="4">
         <v>33</v>
       </c>
-      <c r="C34" t="s">
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35">
+      <c r="C35">
         <v>191066</v>
       </c>
-      <c r="B35" s="4">
+      <c r="D35" s="4">
         <v>34</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36">
+      <c r="C36">
         <v>191067</v>
       </c>
-      <c r="B36" s="4">
+      <c r="D36" s="4">
         <v>35</v>
       </c>
-      <c r="C36" t="s">
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37">
+      <c r="C37">
         <v>191068</v>
       </c>
-      <c r="B37" s="4">
+      <c r="D37" s="4">
         <v>36</v>
       </c>
-      <c r="C37" t="s">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="4">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38">
+      <c r="C38">
         <v>191069</v>
       </c>
-      <c r="B38" s="4">
+      <c r="D38" s="4">
         <v>37</v>
       </c>
-      <c r="C38" t="s">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39">
+      <c r="C39">
         <v>191070</v>
       </c>
-      <c r="B39" s="4">
+      <c r="D39" s="4">
         <v>38</v>
       </c>
-      <c r="C39" t="s">
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="4">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40">
+      <c r="C40">
         <v>191071</v>
       </c>
-      <c r="B40" s="4">
+      <c r="D40" s="4">
         <v>39</v>
       </c>
-      <c r="C40" t="s">
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41">
+      <c r="C41">
         <v>191072</v>
       </c>
-      <c r="B41" s="4">
+      <c r="D41" s="4">
         <v>40</v>
       </c>
-      <c r="C41" t="s">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="4">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42">
+      <c r="C42">
         <v>191073</v>
       </c>
-      <c r="B42" s="4">
+      <c r="D42" s="4">
         <v>41</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="4">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43">
+      <c r="C43">
         <v>191074</v>
       </c>
-      <c r="B43" s="4">
+      <c r="D43" s="4">
         <v>42</v>
       </c>
-      <c r="C43" t="s">
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="4">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44">
+      <c r="C44">
         <v>191075</v>
       </c>
-      <c r="B44" s="4">
+      <c r="D44" s="4">
         <v>43</v>
       </c>
-      <c r="C44" t="s">
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="4">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45">
+      <c r="C45">
         <v>191076</v>
       </c>
-      <c r="B45" s="4">
+      <c r="D45" s="4">
         <v>44</v>
       </c>
-      <c r="C45" t="s">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="4">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46">
+      <c r="C46">
         <v>191077</v>
       </c>
-      <c r="B46" s="4">
+      <c r="D46" s="4">
         <v>45</v>
       </c>
-      <c r="C46" t="s">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="4">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47">
+      <c r="C47">
         <v>191078</v>
       </c>
-      <c r="B47" s="4">
+      <c r="D47" s="4">
         <v>46</v>
       </c>
-      <c r="C47" t="s">
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="4">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48">
+      <c r="C48">
         <v>191079</v>
       </c>
-      <c r="B48" s="4">
+      <c r="D48" s="4">
         <v>47</v>
       </c>
-      <c r="C48" t="s">
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="4">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49">
+      <c r="C49">
         <v>191080</v>
       </c>
-      <c r="B49" s="4">
+      <c r="D49" s="4">
         <v>48</v>
       </c>
-      <c r="C49" t="s">
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="4">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50">
+      <c r="C50">
         <v>191081</v>
       </c>
-      <c r="B50" s="4">
+      <c r="D50" s="4">
         <v>49</v>
       </c>
-      <c r="C50" t="s">
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="4">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51">
+      <c r="C51">
         <v>191082</v>
       </c>
-      <c r="B51" s="4">
+      <c r="D51" s="4">
         <v>50</v>
       </c>
-      <c r="C51" t="s">
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="4">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52">
+      <c r="C52">
         <v>191083</v>
       </c>
-      <c r="B52" s="4">
+      <c r="D52" s="4">
         <v>51</v>
       </c>
-      <c r="C52" t="s">
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="4">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53">
+      <c r="C53">
         <v>191084</v>
       </c>
-      <c r="B53" s="4">
+      <c r="D53" s="4">
         <v>52</v>
       </c>
-      <c r="C53" t="s">
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="4">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54">
+      <c r="C54">
         <v>191085</v>
       </c>
-      <c r="B54" s="4">
+      <c r="D54" s="4">
         <v>53</v>
       </c>
-      <c r="C54" t="s">
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="4">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55">
+      <c r="C55">
         <v>191086</v>
       </c>
-      <c r="B55" s="4">
+      <c r="D55" s="4">
         <v>54</v>
       </c>
-      <c r="C55" t="s">
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="4">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56">
+      <c r="C56">
         <v>191087</v>
       </c>
-      <c r="B56" s="4">
+      <c r="D56" s="4">
         <v>55</v>
       </c>
-      <c r="C56" t="s">
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="4">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57">
+      <c r="C57">
         <v>191088</v>
       </c>
-      <c r="B57" s="4">
+      <c r="D57" s="4">
         <v>56</v>
       </c>
-      <c r="C57" t="s">
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="4">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58">
+      <c r="C58">
         <v>191089</v>
       </c>
-      <c r="B58" s="4">
+      <c r="D58" s="4">
         <v>57</v>
       </c>
-      <c r="C58" t="s">
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="4">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59">
+      <c r="C59">
         <v>191090</v>
       </c>
-      <c r="B59" s="4">
+      <c r="D59" s="4">
         <v>58</v>
       </c>
-      <c r="C59" t="s">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="4">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
         <v>506</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60">
+      <c r="C60">
         <v>191091</v>
       </c>
-      <c r="B60" s="4">
+      <c r="D60" s="4">
         <v>59</v>
       </c>
-      <c r="C60" t="s">
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="4">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61">
+      <c r="C61">
         <v>191092</v>
       </c>
-      <c r="B61" s="4">
+      <c r="D61" s="4">
         <v>60</v>
       </c>
-      <c r="C61" t="s">
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="4">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62">
+      <c r="C62">
         <v>191164</v>
       </c>
-      <c r="B62" s="4">
+      <c r="D62" s="4">
         <v>61</v>
       </c>
-      <c r="C62" t="s">
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="4">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63">
+      <c r="C63">
         <v>191165</v>
       </c>
-      <c r="B63" s="4">
+      <c r="D63" s="4">
         <v>62</v>
       </c>
-      <c r="C63" t="s">
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="4">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
         <v>510</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64">
+      <c r="C64">
         <v>191166</v>
       </c>
-      <c r="B64" s="4">
+      <c r="D64" s="4">
         <v>63</v>
       </c>
-      <c r="C64" t="s">
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="4">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65">
+      <c r="C65">
         <v>191167</v>
       </c>
-      <c r="B65" s="4">
+      <c r="D65" s="4">
         <v>64</v>
       </c>
-      <c r="C65" t="s">
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="4">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66">
+      <c r="C66">
         <v>191168</v>
       </c>
-      <c r="B66" s="4">
+      <c r="D66" s="4">
         <v>65</v>
       </c>
-      <c r="C66" t="s">
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="4">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
         <v>513</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67">
+      <c r="C67">
         <v>191169</v>
       </c>
-      <c r="B67" s="4">
+      <c r="D67" s="4">
         <v>66</v>
       </c>
-      <c r="C67" t="s">
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="4">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68">
+      <c r="C68">
         <v>191170</v>
       </c>
-      <c r="B68" s="4">
+      <c r="D68" s="4">
         <v>67</v>
       </c>
-      <c r="C68" t="s">
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="4">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69">
+      <c r="C69">
         <v>191171</v>
       </c>
-      <c r="B69" s="4">
+      <c r="D69" s="4">
         <v>68</v>
       </c>
-      <c r="C69" t="s">
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="4">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
         <v>516</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70">
+      <c r="C70">
         <v>191172</v>
       </c>
-      <c r="B70" s="4">
+      <c r="D70" s="4">
         <v>69</v>
       </c>
-      <c r="C70" t="s">
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="4">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71">
+      <c r="C71">
         <v>191173</v>
       </c>
-      <c r="B71" s="4">
+      <c r="D71" s="4">
         <v>70</v>
       </c>
-      <c r="C71" t="s">
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="4">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
         <v>518</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72">
+      <c r="C72">
         <v>191174</v>
       </c>
-      <c r="B72" s="4">
+      <c r="D72" s="4">
         <v>71</v>
       </c>
-      <c r="C72" t="s">
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="4">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73">
+      <c r="C73">
         <v>191175</v>
       </c>
-      <c r="B73" s="4">
+      <c r="D73" s="4">
         <v>72</v>
-      </c>
-      <c r="C73" t="s">
-        <v>520</v>
       </c>
     </row>
   </sheetData>
